--- a/tests/reference_data/test_scenario_flowsolver_virtual_flows.xlsx
+++ b/tests/reference_data/test_scenario_flowsolver_virtual_flows.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40992BB-1DC4-4042-9272-12B7D82DA46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A9B089-79D7-40B9-94FC-C62AA1201125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="2610" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-25635" yWindow="2265" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -906,7 +906,22 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -1894,42 +1909,42 @@
   </sheetData>
   <autoFilter ref="B6:E6" xr:uid="{89FFA668-DA1A-459B-BD42-D0D7F7709F0D}"/>
   <conditionalFormatting sqref="C15:C16">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="notEqual">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:C22">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="notEqual">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="notEqual">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C29">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="notEqual">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37:C38">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3067,12 +3082,26 @@
       <c r="J2" t="s">
         <v>99</v>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
+      <c r="K2" s="24" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2" xr:uid="{E6C6FFDE-D5B6-4DA6-ABA9-6CDA5952B7D3}">
+      <formula1>Boolean</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -3330,27 +3359,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
-    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100806C55B750152A459818B636E97A41C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="74fd9cb75cef04cf26a1ff9ddef01b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xmlns:ns3="145cc194-9bea-4db6-b116-a042a4529fcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afbcbfdd38894bc2ff0644b00c8ec680" ns2:_="" ns3:_="">
     <xsd:import namespace="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
@@ -3613,10 +3621,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
+    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
+    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3639,20 +3679,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
-    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>